--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487597_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487597_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.2567</v>
+        <v>6.7058</v>
       </c>
       <c r="E2" t="n">
-        <v>9.3644</v>
+        <v>6.9225</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1077</v>
+        <v>-0.2167</v>
       </c>
       <c r="G2" t="n">
         <v>3.4529</v>
@@ -610,13 +610,13 @@
         <v>1.7463</v>
       </c>
       <c r="S2" t="n">
-        <v>5.386</v>
+        <v>2.835</v>
       </c>
       <c r="T2" t="n">
-        <v>4.6242</v>
+        <v>2.1823</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7618</v>
+        <v>0.6528</v>
       </c>
       <c r="V2" t="n">
         <v>0.6119</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.7157</v>
+        <v>5.8693</v>
       </c>
       <c r="E3" t="n">
-        <v>6.1946</v>
+        <v>5.2937</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5211</v>
+        <v>0.5756</v>
       </c>
       <c r="G3" t="n">
         <v>2.0817</v>
@@ -688,13 +688,13 @@
         <v>1.3582</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7221</v>
+        <v>0.8757</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7238</v>
+        <v>0.8229</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0018</v>
+        <v>0.0527</v>
       </c>
       <c r="V3" t="n">
         <v>1.5537</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.367</v>
+        <v>3.3858</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4162</v>
+        <v>2.8166</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9508</v>
+        <v>0.5693</v>
       </c>
       <c r="G4" t="n">
         <v>1.4049</v>
@@ -766,13 +766,13 @@
         <v>1.5523</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1561</v>
+        <v>0.175</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4722</v>
+        <v>-0.0718</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6283</v>
+        <v>0.2468</v>
       </c>
       <c r="V4" t="n">
         <v>1.2239</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.954</v>
+        <v>2.0997</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9161</v>
+        <v>1.1163</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0379</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="G5" t="n">
         <v>1.166</v>
@@ -844,13 +844,13 @@
         <v>0.9702</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1821</v>
+        <v>-0.0364</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4845</v>
+        <v>-0.2843</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3024</v>
+        <v>0.2479</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0291</v>
+        <v>1.4539</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7067</v>
+        <v>-0.1456</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7358</v>
+        <v>1.5995</v>
       </c>
       <c r="G6" t="n">
         <v>-0.6152</v>
@@ -922,13 +922,13 @@
         <v>1.5523</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2378</v>
+        <v>0.187</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5933</v>
+        <v>-0.0323</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3556</v>
+        <v>0.2193</v>
       </c>
       <c r="V6" t="n">
         <v>0.3299</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. TCHIRAKADZE</t>
+          <t>J. VAQUERO PASCUAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.804</v>
+        <v>1.1129</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8566</v>
+        <v>0.8691</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6606</v>
+        <v>0.2438</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0194</v>
+        <v>-2.4248</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3922</v>
+        <v>0.4581</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4115</v>
+        <v>-2.8829</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1565</v>
+        <v>-0.5696</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5108</v>
+        <v>1.3512</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6673</v>
+        <v>-1.9208</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1371</v>
+        <v>-1.8552</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1187</v>
+        <v>-0.8931</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2558</v>
+        <v>-0.9621</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.5821</v>
+        <v>-1.7463</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9403</v>
+        <v>-3.8806</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3582</v>
+        <v>2.1344</v>
       </c>
       <c r="S7" t="n">
-        <v>1.7831</v>
+        <v>1.0004</v>
       </c>
       <c r="T7" t="n">
-        <v>1.3358</v>
+        <v>0.7537</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4473</v>
+        <v>0.2468</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3776</v>
+        <v>4.2836</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.0955</v>
+        <v>4.5656</v>
       </c>
       <c r="X7" t="n">
         <v>-0.2821</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. VAQUERO PASCUAL</t>
+          <t>G. TCHIRAKADZE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0395</v>
+        <v>0.5732</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0683</v>
+        <v>-1.1964</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0287</v>
+        <v>1.7696</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.4248</v>
+        <v>-0.0194</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4581</v>
+        <v>0.3922</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.8829</v>
+        <v>-0.4115</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5696</v>
+        <v>-0.1565</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3512</v>
+        <v>0.5108</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.9208</v>
+        <v>-0.6673</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.8552</v>
+        <v>0.1371</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8931</v>
+        <v>-0.1187</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9621</v>
+        <v>0.2558</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.7463</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.8806</v>
+        <v>-1.9403</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1344</v>
+        <v>1.3582</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.07290000000000001</v>
+        <v>1.5523</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0471</v>
+        <v>0.9959</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0258</v>
+        <v>0.5563</v>
       </c>
       <c r="V8" t="n">
-        <v>4.2836</v>
+        <v>-0.3776</v>
       </c>
       <c r="W8" t="n">
-        <v>4.5656</v>
+        <v>-0.0955</v>
       </c>
       <c r="X8" t="n">
         <v>-0.2821</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8057</v>
+        <v>-0.4326</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3544</v>
+        <v>0.046</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4513</v>
+        <v>-0.4786</v>
       </c>
       <c r="G9" t="n">
         <v>-0.8972</v>
@@ -1156,13 +1156,13 @@
         <v>1.3582</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0428</v>
+        <v>0.3303</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5933</v>
+        <v>-0.1929</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5505</v>
+        <v>0.5232</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2239</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.084</v>
+        <v>-2.5224</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2029</v>
+        <v>-1.3416</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8811</v>
+        <v>-1.1809</v>
       </c>
       <c r="G10" t="n">
         <v>-0.4656</v>
@@ -1234,13 +1234,13 @@
         <v>1.1642</v>
       </c>
       <c r="S10" t="n">
-        <v>1.0115</v>
+        <v>1.573</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1951</v>
+        <v>1.0565</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8163</v>
+        <v>0.5165</v>
       </c>
       <c r="V10" t="n">
         <v>-1.8836</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9116</v>
+        <v>-2.8144</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6835</v>
+        <v>-2.0224</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2281</v>
+        <v>-0.792</v>
       </c>
       <c r="G11" t="n">
         <v>-1.3252</v>
@@ -1312,13 +1312,13 @@
         <v>1.7463</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5464</v>
+        <v>1.6437</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4991</v>
+        <v>1.1602</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0474</v>
+        <v>0.4834</v>
       </c>
       <c r="V11" t="n">
         <v>0.9418</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.9518</v>
+        <v>-3.7154</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.6021</v>
+        <v>-1.502</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3496</v>
+        <v>-2.2134</v>
       </c>
       <c r="G12" t="n">
         <v>-1.2366</v>
@@ -1390,13 +1390,13 @@
         <v>0.5821</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4912</v>
+        <v>-0.2549</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1088</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3824</v>
+        <v>-0.2462</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8358</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.4129</v>
+        <v>11.7158</v>
       </c>
       <c r="E13" t="n">
-        <v>10.5534</v>
+        <v>10.8562</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8597000000000001</v>
+        <v>0.8595999999999995</v>
       </c>
       <c r="G13" t="n">
         <v>1.121499999999999</v>
@@ -1468,13 +1468,13 @@
         <v>15.5227</v>
       </c>
       <c r="S13" t="n">
-        <v>9.578400000000002</v>
+        <v>9.8811</v>
       </c>
       <c r="T13" t="n">
-        <v>6.078800000000001</v>
+        <v>6.3815</v>
       </c>
       <c r="U13" t="n">
-        <v>3.4996</v>
+        <v>3.4995</v>
       </c>
       <c r="V13" t="n">
         <v>3.623900000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.3277</v>
+        <v>7.7798</v>
       </c>
       <c r="E14" t="n">
-        <v>5.5241</v>
+        <v>5.9245</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8036</v>
+        <v>1.8553</v>
       </c>
       <c r="G14" t="n">
         <v>6.6913</v>
@@ -1546,13 +1546,13 @@
         <v>2.9105</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3039</v>
+        <v>-0.8518</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8838</v>
+        <v>-0.4834</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4201</v>
+        <v>-0.3684</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8961</v>
+        <v>5.1001</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2215</v>
+        <v>4.0223</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6746</v>
+        <v>1.0778</v>
       </c>
       <c r="G15" t="n">
         <v>-1.6435</v>
@@ -1624,13 +1624,13 @@
         <v>3.6866</v>
       </c>
       <c r="S15" t="n">
-        <v>-3.0619</v>
+        <v>-1.8579</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.586</v>
+        <v>-0.7852</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.4759</v>
+        <v>-1.0727</v>
       </c>
       <c r="V15" t="n">
         <v>5.8851</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.927</v>
+        <v>2.0839</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9159</v>
+        <v>-0.0851</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0111</v>
+        <v>2.169</v>
       </c>
       <c r="G16" t="n">
         <v>3.5869</v>
@@ -1702,13 +1702,13 @@
         <v>2.9105</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9221</v>
+        <v>0.0791</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8882</v>
+        <v>-0.1128</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0339</v>
+        <v>0.1918</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6119</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3307</v>
+        <v>-0.131</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7421</v>
+        <v>-0.8421999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4114</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="G17" t="n">
         <v>-0.7252999999999999</v>
@@ -1780,13 +1780,13 @@
         <v>2.7164</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.5577</v>
+        <v>-1.3579</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5193</v>
+        <v>-0.6194</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0383</v>
+        <v>-0.7385</v>
       </c>
       <c r="V17" t="n">
         <v>1.1761</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6654</v>
+        <v>-0.5836</v>
       </c>
       <c r="E18" t="n">
         <v>0.5917</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.257</v>
+        <v>-1.1752</v>
       </c>
       <c r="G18" t="n">
         <v>0.698</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1395</v>
+        <v>-0.0578</v>
       </c>
       <c r="T18" t="n">
         <v>-0.0606</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.079</v>
+        <v>0.0028</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2239</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.6683</v>
+        <v>-2.9136</v>
       </c>
       <c r="E19" t="n">
         <v>-0.4255</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2428</v>
+        <v>-2.4881</v>
       </c>
       <c r="G19" t="n">
         <v>-1.5346</v>
@@ -1936,13 +1936,13 @@
         <v>1.3582</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5516</v>
+        <v>-0.7969000000000001</v>
       </c>
       <c r="T19" t="n">
         <v>-0.2647</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2869</v>
+        <v>-0.5322</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.4759</v>
+        <v>-3.4214</v>
       </c>
       <c r="E20" t="n">
         <v>-1.69</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7859</v>
+        <v>-1.7313</v>
       </c>
       <c r="G20" t="n">
         <v>-0.4025</v>
@@ -2014,13 +2014,13 @@
         <v>0.3881</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9092</v>
+        <v>-0.8546</v>
       </c>
       <c r="T20" t="n">
         <v>-0.4116</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4975</v>
+        <v>-0.443</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6119</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. LOBATO ANDRADE</t>
+          <t>P. DOMINGUEZ LORENZO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6722</v>
+        <v>-3.5035</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7247</v>
+        <v>-2.9722</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.9476</v>
+        <v>-0.5313</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.6554</v>
+        <v>-2.112</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6148</v>
+        <v>-2.0597</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0406</v>
+        <v>-0.0523</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6786</v>
+        <v>-1.5089</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1153</v>
+        <v>-0.9227</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5633</v>
+        <v>-0.5861</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9767</v>
+        <v>-0.6031</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.4995</v>
+        <v>-1.137</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.5339</v>
       </c>
       <c r="P21" t="n">
-        <v>1.7463</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R21" t="n">
-        <v>2.7164</v>
+        <v>0.3881</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4726</v>
+        <v>-0.8095</v>
       </c>
       <c r="T21" t="n">
-        <v>0.9241</v>
+        <v>-0.4932</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4515</v>
+        <v>-0.3163</v>
       </c>
       <c r="V21" t="n">
-        <v>-4.2358</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-4.2358</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. DOMINGUEZ LORENZO</t>
+          <t>R. LOPEZ RIVERA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7127</v>
+        <v>-4.6852</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0723</v>
+        <v>-3.1241</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6403</v>
+        <v>-1.5611</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.112</v>
+        <v>-4.5887</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.0597</v>
+        <v>-3.2947</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0523</v>
+        <v>-1.2941</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.5089</v>
+        <v>-2.8223</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9227</v>
+        <v>-0.8609</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5861</v>
+        <v>-1.9614</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6031</v>
+        <v>-1.7664</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.137</v>
+        <v>-2.4337</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5339</v>
+        <v>0.6673</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.5821</v>
+        <v>0.9702</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3881</v>
+        <v>0.9702</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0186</v>
+        <v>-0.7846</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5933</v>
+        <v>-0.3017</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4253</v>
+        <v>-0.4828</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E. BOADA MONTESDEOCA</t>
+          <t>J. LOBATO ANDRADE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.4953</v>
+        <v>-4.7968</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.9338</v>
+        <v>-1.6256</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.5615</v>
+        <v>-3.1712</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5643</v>
+        <v>-1.6554</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2974</v>
+        <v>-1.6148</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2669</v>
+        <v>-0.0406</v>
       </c>
       <c r="J23" t="n">
-        <v>1.9567</v>
+        <v>-0.6786</v>
       </c>
       <c r="K23" t="n">
-        <v>1.9567</v>
+        <v>-0.1153</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>-0.5633</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3924</v>
+        <v>-0.9767</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.6593</v>
+        <v>-1.4995</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2669</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.5523</v>
+        <v>1.7463</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3881</v>
+        <v>2.7164</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.788</v>
+        <v>-0.6519</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2905</v>
+        <v>0.0232</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4975</v>
+        <v>-0.6751</v>
       </c>
       <c r="V23" t="n">
-        <v>-3.7194</v>
+        <v>-4.2358</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.6597</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-3.0597</v>
+        <v>-4.2358</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R. LOPEZ RIVERA</t>
+          <t>E. BOADA MONTESDEOCA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.5433</v>
+        <v>-5.007</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.5245</v>
+        <v>-0.6335</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.0189</v>
+        <v>-4.3735</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.5887</v>
+        <v>0.5643</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.2947</v>
+        <v>0.2974</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.2941</v>
+        <v>0.2669</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.8223</v>
+        <v>1.9567</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.8609</v>
+        <v>1.9567</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.9614</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.7664</v>
+        <v>-1.3924</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.4337</v>
+        <v>-1.6593</v>
       </c>
       <c r="O24" t="n">
-        <v>0.6673</v>
+        <v>0.2669</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9702</v>
+        <v>-1.5523</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9702</v>
+        <v>0.3881</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.6427</v>
+        <v>-0.2997</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7020999999999999</v>
+        <v>0.0098</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.9405</v>
+        <v>-0.3095</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.2821</v>
+        <v>-3.7194</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>-0.6597</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.2821</v>
+        <v>-3.0597</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-11.413</v>
+        <v>-10.0783</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.8597000000000006</v>
+        <v>-0.8597000000000012</v>
       </c>
       <c r="F25" t="n">
-        <v>-10.5533</v>
+        <v>-9.218399999999999</v>
       </c>
       <c r="G25" t="n">
         <v>-1.121499999999999</v>
@@ -2380,10 +2380,10 @@
         <v>11.6223</v>
       </c>
       <c r="K25" t="n">
-        <v>6.756000000000001</v>
+        <v>6.756</v>
       </c>
       <c r="L25" t="n">
-        <v>4.866299999999999</v>
+        <v>4.8663</v>
       </c>
       <c r="M25" t="n">
         <v>-12.7436</v>
@@ -2404,13 +2404,13 @@
         <v>18.4331</v>
       </c>
       <c r="S25" t="n">
-        <v>-9.5784</v>
+        <v>-8.243500000000001</v>
       </c>
       <c r="T25" t="n">
         <v>-3.4996</v>
       </c>
       <c r="U25" t="n">
-        <v>-6.0786</v>
+        <v>-4.7439</v>
       </c>
       <c r="V25" t="n">
         <v>-3.6238</v>
